--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:27:26+00:00</t>
+          <t>2026-05-10T00:26:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:26:56+00:00</t>
+          <t>2026-05-11T00:27:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:19+00:00</t>
+          <t>2026-05-12T00:27:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:27:33+00:00</t>
+          <t>2026-05-13T00:29:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:29:54+00:00</t>
+          <t>2026-05-14T00:30:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:30:52+00:00</t>
+          <t>2026-05-15T00:28:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:28:40+00:00</t>
+          <t>2026-05-16T00:27:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:27:11+00:00</t>
+          <t>2026-05-17T00:28:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T00:28:31+00:00</t>
+          <t>2026-05-18T00:29:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:04+00:00</t>
+          <t>2026-05-19T00:32:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:10+00:00</t>
+          <t>2026-05-20T00:33:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:33:47+00:00</t>
+          <t>2026-05-21T00:34:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21T00:34:39+00:00</t>
+          <t>2026-05-22T00:31:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:31:46+00:00</t>
+          <t>2026-05-23T00:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T00:32:34+00:00</t>
+          <t>2026-05-24T00:30:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:30:12+00:00</t>
+          <t>2026-05-25T00:33:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T00:33:33+00:00</t>
+          <t>2026-05-26T00:30:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:30:24+00:00</t>
+          <t>2026-05-27T00:33:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27T00:33:09+00:00</t>
+          <t>2026-05-28T00:29:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:29:41+00:00</t>
+          <t>2026-05-29T00:35:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29T00:35:47+00:00</t>
+          <t>2026-05-30T00:32:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30T00:32:17+00:00</t>
+          <t>2026-05-31T00:33:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31T00:33:30+00:00</t>
+          <t>2026-06-01T00:34:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:34:34+00:00</t>
+          <t>2026-06-02T00:39:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:39:57+00:00</t>
+          <t>2026-06-03T00:43:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:43:21+00:00</t>
+          <t>2026-06-04T00:43:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:43:04+00:00</t>
+          <t>2026-06-05T00:36:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05T00:36:16+00:00</t>
+          <t>2026-06-06T00:34:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06T00:34:19+00:00</t>
+          <t>2026-06-07T00:35:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:35:14+00:00</t>
+          <t>2026-06-08T00:36:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:36:52+00:00</t>
+          <t>2026-06-09T00:31:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:31:56+00:00</t>
+          <t>2026-06-10T00:37:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:37:57+00:00</t>
+          <t>2026-06-11T00:38:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:38:25+00:00</t>
+          <t>2026-06-12T00:39:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:39:38+00:00</t>
+          <t>2026-06-13T00:38:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:38:58+00:00</t>
+          <t>2026-06-14T00:37:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:37:36+00:00</t>
+          <t>2026-06-15T00:38:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:38:44+00:00</t>
+          <t>2026-06-16T00:44:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:44:04+00:00</t>
+          <t>2026-06-17T00:39:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:39:21+00:00</t>
+          <t>2026-06-18T00:43:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:43:37+00:00</t>
+          <t>2026-06-19T00:43:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:43:22+00:00</t>
+          <t>2026-06-20T00:34:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:34:18+00:00</t>
+          <t>2026-06-21T00:38:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21T00:38:47+00:00</t>
+          <t>2026-06-22T00:37:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:37:48+00:00</t>
+          <t>2026-06-23T00:35:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23T00:35:33+00:00</t>
+          <t>2026-06-24T00:29:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24T00:29:51+00:00</t>
+          <t>2026-06-25T00:34:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:34:52+00:00</t>
+          <t>2026-06-26T00:41:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26T00:41:25+00:00</t>
+          <t>2026-06-27T00:32:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:32:45+00:00</t>
+          <t>2026-06-28T00:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:32:34+00:00</t>
+          <t>2026-06-29T00:34:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29T00:34:54+00:00</t>
+          <t>2026-06-30T00:33:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:33:10+00:00</t>
+          <t>2026-07-01T00:38:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01T00:38:09+00:00</t>
+          <t>2026-07-02T00:33:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02T00:33:15+00:00</t>
+          <t>2026-07-03T02:05:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:05:09+00:00</t>
+          <t>2026-07-04T02:02:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04T02:02:48+00:00</t>
+          <t>2026-07-05T02:10:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05T02:10:50+00:00</t>
+          <t>2026-07-06T02:15:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06T02:15:36+00:00</t>
+          <t>2026-07-07T02:11:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07T02:11:06+00:00</t>
+          <t>2026-07-08T01:52:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08T01:52:30+00:00</t>
+          <t>2026-07-09T02:05:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09T02:05:32+00:00</t>
+          <t>2026-07-10T02:04:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10T02:04:03+00:00</t>
+          <t>2026-07-11T01:50:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11T01:50:53+00:00</t>
+          <t>2026-07-12T01:53:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:53:25+00:00</t>
+          <t>2026-07-13T01:56:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13T01:56:05+00:00</t>
+          <t>2026-07-14T01:43:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14T01:43:09+00:00</t>
+          <t>2026-07-15T01:29:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15T01:29:00+00:00</t>
+          <t>2026-07-16T01:49:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16T01:49:28+00:00</t>
+          <t>2026-07-17T01:52:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17T01:52:52+00:00</t>
+          <t>2026-07-18T01:43:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18T01:43:36+00:00</t>
+          <t>2026-07-19T01:51:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19T01:51:40+00:00</t>
+          <t>2026-07-20T03:25:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20T03:25:18+00:00</t>
+          <t>2026-07-21T01:55:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21T01:55:00+00:00</t>
+          <t>2026-07-22T01:50:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22T01:50:18+00:00</t>
+          <t>2026-07-23T01:59:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23T01:59:00+00:00</t>
+          <t>2026-07-24T01:54:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24T01:54:28+00:00</t>
+          <t>2026-07-25T01:53:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25T01:53:07+00:00</t>
+          <t>2026-07-26T01:56:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26T01:56:35+00:00</t>
+          <t>2026-07-27T02:07:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27T02:07:06+00:00</t>
+          <t>2026-07-28T01:46:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28T01:46:42+00:00</t>
+          <t>2026-07-29T01:48:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29T01:48:26+00:00</t>
+          <t>2026-07-30T01:31:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30T01:31:25+00:00</t>
+          <t>2026-07-31T01:58:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31T01:58:24+00:00</t>
+          <t>2026-08-01T01:58:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01T01:58:56+00:00</t>
+          <t>2026-08-02T01:55:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T01:55:00+00:00</t>
+          <t>2026-08-03T01:57:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T01:57:39+00:00</t>
+          <t>2026-08-04T01:44:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T01:44:31+00:00</t>
+          <t>2026-08-05T01:45:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05T01:45:41+00:00</t>
+          <t>2026-08-06T01:46:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06T01:46:01+00:00</t>
+          <t>2026-08-07T02:10:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07T02:10:29+00:00</t>
+          <t>2026-08-08T00:57:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08T00:57:37+00:00</t>
+          <t>2026-08-09T01:01:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09T01:01:36+00:00</t>
+          <t>2026-08-10T01:03:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10T01:03:50+00:00</t>
+          <t>2026-08-11T01:02:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11T01:02:20+00:00</t>
+          <t>2026-08-12T01:09:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12T01:09:29+00:00</t>
+          <t>2026-08-13T01:11:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13T01:11:31+00:00</t>
+          <t>2026-08-14T01:10:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14T01:10:11+00:00</t>
+          <t>2026-08-15T00:43:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15T00:43:45+00:00</t>
+          <t>2026-08-16T00:44:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16T00:44:42+00:00</t>
+          <t>2026-08-17T00:42:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T00:42:50+00:00</t>
+          <t>2026-08-17T06:42:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:42:58+00:00</t>
+          <t>2026-08-17T06:55:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:55:25+00:00</t>
+          <t>2026-08-17T07:42:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:42:46+00:00</t>
+          <t>2026-08-17T08:00:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:00:08+00:00</t>
+          <t>2026-08-17T08:13:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:13:39+00:00</t>
+          <t>2026-08-17T08:28:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:28:55+00:00</t>
+          <t>2026-08-17T09:21:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:21:26+00:00</t>
+          <t>2026-08-17T09:26:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:26:53+00:00</t>
+          <t>2026-08-17T10:45:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:45:33+00:00</t>
+          <t>2026-08-17T12:52:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:52:00+00:00</t>
+          <t>2026-08-17T23:14:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:14:27+00:00</t>
+          <t>2026-08-18T05:52:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:52:54+00:00</t>
+          <t>2026-08-18T23:14:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T23:14:41+00:00</t>
+          <t>2026-08-19T23:15:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:15:18+00:00</t>
+          <t>2026-08-20T23:17:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:17:44+00:00</t>
+          <t>2026-08-21T23:15:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:09+00:00</t>
+          <t>2026-08-22T23:12:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:12:52+00:00</t>
+          <t>2026-08-23T23:12:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:12:32+00:00</t>
+          <t>2026-08-24T23:15:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:15:52+00:00</t>
+          <t>2026-08-25T23:17:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:17:45+00:00</t>
+          <t>2026-08-27T04:09:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:09:37+00:00</t>
+          <t>2026-08-28T06:26:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:26:27+00:00</t>
+          <t>2026-08-29T03:58:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T03:58:45+00:00</t>
+          <t>2026-08-30T00:56:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:56:05+00:00</t>
+          <t>2026-08-31T01:00:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:00:49+00:00</t>
+          <t>2026-09-01T01:31:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:31:28+00:00</t>
+          <t>2026-09-02T00:41:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:41:23+00:00</t>
+          <t>2026-09-03T00:53:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:53:02+00:00</t>
+          <t>2026-09-04T00:33:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:11+00:00</t>
+          <t>2026-09-05T00:29:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:29:26+00:00</t>
+          <t>2026-09-06T00:24:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:24:05+00:00</t>
+          <t>2026-09-07T00:31:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:31:03+00:00</t>
+          <t>2026-09-07T07:49:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:49:14+00:00</t>
+          <t>2026-09-07T09:42:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:42:47+00:00</t>
+          <t>2026-09-07T11:02:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:02:33+00:00</t>
+          <t>2026-09-08T00:49:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:49:45+00:00</t>
+          <t>2026-09-09T00:53:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:53:29+00:00</t>
+          <t>2026-09-09T01:45:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:45:09+00:00</t>
+          <t>2026-09-09T02:38:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:38:16+00:00</t>
+          <t>2026-09-10T00:43:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:43:53+00:00</t>
+          <t>2026-09-11T00:41:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:41:56+00:00</t>
+          <t>2026-09-12T00:49:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:49:51+00:00</t>
+          <t>2026-09-13T00:30:44+00:00</t>
         </is>
       </c>
     </row>
